--- a/Models/Лошади/results/Лошади - Результаты прогнозов Prophet.xlsx
+++ b/Models/Лошади/results/Лошади - Результаты прогнозов Prophet.xlsx
@@ -478,31 +478,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123.15</v>
+        <v>13.37</v>
       </c>
       <c r="E2" t="n">
-        <v>108.33</v>
+        <v>10.78</v>
       </c>
       <c r="F2" t="n">
-        <v>9.01</v>
+        <v>0.99</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[1540.74, 949.35, 898.19]</t>
+          <t>[997.15, 1295.1, 992.64]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[1655.9, 915.95, 1074.61]</t>
+          <t>[995.56, 1304.96, 1013.53]</t>
         </is>
       </c>
     </row>
@@ -514,31 +514,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>99.31999999999999</v>
+        <v>78.91</v>
       </c>
       <c r="E3" t="n">
-        <v>71.51000000000001</v>
+        <v>54.43</v>
       </c>
       <c r="F3" t="n">
-        <v>6.93</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[954.59, 907.19, 861.02]</t>
+          <t>[1296.46, 993.7, 2077.23]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[915.95, 1074.61, 852.53]</t>
+          <t>[1304.96, 1013.53, 2212.19]</t>
         </is>
       </c>
     </row>
@@ -550,31 +550,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>105.31</v>
+        <v>83.87</v>
       </c>
       <c r="E4" t="n">
-        <v>78.62</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>7.27</v>
+        <v>3.49</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[902.04, 856.88, 1185.48]</t>
+          <t>[992.38, 2074.28, 1916.57]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[1074.61, 852.53, 1126.55]</t>
+          <t>[1013.53, 2212.19, 1876.09]</t>
         </is>
       </c>
     </row>
@@ -586,31 +586,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.88</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>57.51</v>
+        <v>60.64</v>
       </c>
       <c r="F5" t="n">
-        <v>4.14</v>
+        <v>2.87</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[867.61, 1203.87, 2042.89]</t>
+          <t>[2077.22, 1921.58, 1608.86]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[852.53, 1126.55, 2123.03]</t>
+          <t>[2212.19, 1876.09, 1610.32]</t>
         </is>
       </c>
     </row>
@@ -622,31 +622,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69.43000000000001</v>
+        <v>30.34</v>
       </c>
       <c r="E6" t="n">
-        <v>67.12</v>
+        <v>23.31</v>
       </c>
       <c r="F6" t="n">
-        <v>4.81</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[1201.73, 2039.34, 1071.42]</t>
+          <t>[1926.3, 1615.32, 1052.29]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[1126.55, 2123.03, 1113.91]</t>
+          <t>[1876.09, 1610.32, 1067.0]</t>
         </is>
       </c>
     </row>
@@ -658,31 +658,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63.22</v>
+        <v>128.86</v>
       </c>
       <c r="E7" t="n">
-        <v>51.19</v>
+        <v>81.36</v>
       </c>
       <c r="F7" t="n">
-        <v>3.24</v>
+        <v>6.86</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[2026.14, 1063.26, 989.53]</t>
+          <t>[1614.96, 1050.07, 967.79]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[2123.03, 1113.91, 995.56]</t>
+          <t>[1610.32, 1067.0, 1190.29]</t>
         </is>
       </c>
     </row>
@@ -694,31 +694,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27.39</v>
+        <v>131.24</v>
       </c>
       <c r="E8" t="n">
-        <v>20.33</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.77</v>
+        <v>8.31</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[1068.81, 994.34, 1290.28]</t>
+          <t>[1050.73, 967.95, 892.46]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[1113.91, 995.56, 1304.96]</t>
+          <t>[1067.0, 1190.29, 936.82]</t>
         </is>
       </c>
     </row>
@@ -730,31 +730,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.37</v>
+        <v>159</v>
       </c>
       <c r="E9" t="n">
-        <v>10.78</v>
+        <v>140.96</v>
       </c>
       <c r="F9" t="n">
-        <v>0.99</v>
+        <v>12.67</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[997.15, 1295.1, 992.64]</t>
+          <t>[968.18, 892.8, 1225.75]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[995.56, 1304.96, 1013.53]</t>
+          <t>[1190.29, 936.82, 1068.99]</t>
         </is>
       </c>
     </row>
@@ -766,31 +766,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78.91</v>
+        <v>135.45</v>
       </c>
       <c r="E10" t="n">
-        <v>54.43</v>
+        <v>117</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9</v>
+        <v>8.99</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[1296.46, 993.7, 2077.23]</t>
+          <t>[912.9, 1254.64, 2150.15]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[1304.96, 1013.53, 2212.19]</t>
+          <t>[936.82, 1068.99, 2008.72]</t>
         </is>
       </c>
     </row>
@@ -802,31 +802,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83.87</v>
+        <v>151.79</v>
       </c>
       <c r="E11" t="n">
-        <v>66.51000000000001</v>
+        <v>146.11</v>
       </c>
       <c r="F11" t="n">
-        <v>3.49</v>
+        <v>11.48</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[992.38, 2074.28, 1916.57]</t>
+          <t>[1261.34, 2162.26, 1142.5]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[1013.53, 2212.19, 1876.09]</t>
+          <t>[1068.99, 2008.72, 1050.06]</t>
         </is>
       </c>
     </row>
@@ -838,31 +838,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>130.56</v>
+        <v>209.36</v>
       </c>
       <c r="E12" t="n">
-        <v>123.63</v>
+        <v>165.34</v>
       </c>
       <c r="F12" t="n">
-        <v>9.27</v>
+        <v>9.18</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[1447.57, 839.75, 1713.55]</t>
+          <t>[967.9, 1452.63, 1741.48]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[1595.0, 775.1, 1554.73]</t>
+          <t>[973.73, 1772.95, 1911.34]</t>
         </is>
       </c>
     </row>
@@ -874,31 +874,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>126.67</v>
+        <v>456.86</v>
       </c>
       <c r="E13" t="n">
-        <v>115.76</v>
+        <v>396.72</v>
       </c>
       <c r="F13" t="n">
-        <v>9.199999999999999</v>
+        <v>16.43</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[848.64, 1742.86, 1336.87]</t>
+          <t>[1454.97, 1744.24, 2415.05]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[775.1, 1554.73, 1422.49]</t>
+          <t>[1772.95, 1911.34, 3120.12]</t>
         </is>
       </c>
     </row>
@@ -910,31 +910,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>118.54</v>
+        <v>438.27</v>
       </c>
       <c r="E14" t="n">
-        <v>113.77</v>
+        <v>379.33</v>
       </c>
       <c r="F14" t="n">
-        <v>7.67</v>
+        <v>12</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[1711.67, 1314.11, 1362.44]</t>
+          <t>[1762.23, 2445.31, 5086.33]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[1554.73, 1422.49, 1438.45]</t>
+          <t>[1911.34, 3120.12, 4772.26]</t>
         </is>
       </c>
     </row>
@@ -946,31 +946,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>253.73</v>
+        <v>444.05</v>
       </c>
       <c r="E15" t="n">
-        <v>202.38</v>
+        <v>395.3</v>
       </c>
       <c r="F15" t="n">
-        <v>9.83</v>
+        <v>13.28</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[1317.61, 1354.65, 2151.43]</t>
+          <t>[2450.52, 5100.75, 1819.91]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[1422.49, 1438.45, 2569.91]</t>
+          <t>[3120.12, 4772.26, 1632.1]</t>
         </is>
       </c>
     </row>
@@ -982,31 +982,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>270.84</v>
+        <v>260.3</v>
       </c>
       <c r="E16" t="n">
-        <v>226.5</v>
+        <v>203.33</v>
       </c>
       <c r="F16" t="n">
-        <v>12.23</v>
+        <v>7.11</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[1368.18, 2143.77, 1020.32]</t>
+          <t>[5170.51, 1843.46, 834.07]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[1438.45, 2569.91, 1203.41]</t>
+          <t>[4772.26, 1632.1, 834.45]</t>
         </is>
       </c>
     </row>
@@ -1018,31 +1018,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>249.25</v>
+        <v>129.49</v>
       </c>
       <c r="E17" t="n">
-        <v>197.95</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>10.8</v>
+        <v>5.71</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[2174.18, 1033.1, 945.91]</t>
+          <t>[1846.36, 833.28, 1781.48]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[2569.91, 1203.41, 973.73]</t>
+          <t>[1632.1, 834.45, 1715.21]</t>
         </is>
       </c>
     </row>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>217.84</v>
+        <v>172.26</v>
       </c>
       <c r="E18" t="n">
-        <v>173.99</v>
+        <v>116.76</v>
       </c>
       <c r="F18" t="n">
-        <v>11.56</v>
+        <v>6.86</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[1042.06, 953.57, 1432.48]</t>
+          <t>[825.16, 1761.62, 1462.9]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[1203.41, 973.73, 1772.95]</t>
+          <t>[834.45, 1715.21, 1757.48]</t>
         </is>
       </c>
     </row>
@@ -1090,31 +1090,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>209.36</v>
+        <v>180.5</v>
       </c>
       <c r="E19" t="n">
-        <v>165.34</v>
+        <v>145.59</v>
       </c>
       <c r="F19" t="n">
-        <v>9.18</v>
+        <v>8.68</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[967.9, 1452.63, 1741.48]</t>
+          <t>[1763.31, 1463.41, 1363.1]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[973.73, 1772.95, 1911.34]</t>
+          <t>[1715.21, 1757.48, 1457.7]</t>
         </is>
       </c>
     </row>
@@ -1126,31 +1126,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>456.86</v>
+        <v>189.88</v>
       </c>
       <c r="E20" t="n">
-        <v>396.72</v>
+        <v>166.56</v>
       </c>
       <c r="F20" t="n">
-        <v>16.43</v>
+        <v>9.24</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[1454.97, 1744.24, 2415.05]</t>
+          <t>[1462.18, 1361.94, 2384.74]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[1772.95, 1911.34, 3120.12]</t>
+          <t>[1757.48, 1457.7, 2493.35]</t>
         </is>
       </c>
     </row>
@@ -1162,31 +1162,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>438.27</v>
+        <v>211.41</v>
       </c>
       <c r="E21" t="n">
-        <v>379.33</v>
+        <v>162.54</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>10.48</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[1762.23, 2445.31, 5086.33]</t>
+          <t>[1387.73, 2429.39, 1115.26]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[1911.34, 3120.12, 4772.26]</t>
+          <t>[1457.7, 2493.35, 1468.96]</t>
         </is>
       </c>
     </row>
@@ -1198,31 +1198,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>655.05</v>
+        <v>526.09</v>
       </c>
       <c r="E22" t="n">
-        <v>527.29</v>
+        <v>449.92</v>
       </c>
       <c r="F22" t="n">
-        <v>48.7</v>
+        <v>22.74</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[770.68, 597.61, 1876.72]</t>
+          <t>[1472.13, 1754.98, 1053.83]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[407.0, 752.27, 2940.25]</t>
+          <t>[1573.54, 2522.07, 1535.1]</t>
         </is>
       </c>
     </row>
@@ -1234,31 +1234,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>790.26</v>
+        <v>602.36</v>
       </c>
       <c r="E23" t="n">
-        <v>663.2</v>
+        <v>591</v>
       </c>
       <c r="F23" t="n">
-        <v>41.66</v>
+        <v>27.3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[564.0, 1711.17, 411.66]</t>
+          <t>[1774.2, 1065.81, 2007.31]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[752.27, 2940.25, 983.9]</t>
+          <t>[2522.07, 1535.1, 2563.15]</t>
         </is>
       </c>
     </row>
@@ -1270,31 +1270,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>759.77</v>
+        <v>1134.14</v>
       </c>
       <c r="E24" t="n">
-        <v>673.47</v>
+        <v>940.03</v>
       </c>
       <c r="F24" t="n">
-        <v>45.91</v>
+        <v>28.62</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[1787.26, 435.8, 426.75]</t>
+          <t>[1077.15, 2037.53, 3331.75]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[2940.25, 983.9, 746.07]</t>
+          <t>[1535.1, 2563.15, 5168.28]</t>
         </is>
       </c>
     </row>
@@ -1306,31 +1306,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>374.97</v>
+        <v>1032.81</v>
       </c>
       <c r="E25" t="n">
-        <v>347.21</v>
+        <v>805.8099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>35.01</v>
+        <v>31.99</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[446.16, 440.78, 1899.09]</t>
+          <t>[2103.99, 3457.07, 796.51]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[983.9, 746.07, 2097.7]</t>
+          <t>[2563.15, 5168.28, 549.47]</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>165.11</v>
+        <v>1002.26</v>
       </c>
       <c r="E26" t="n">
-        <v>132.93</v>
+        <v>705.39</v>
       </c>
       <c r="F26" t="n">
-        <v>18.5</v>
+        <v>33.82</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[474.82, 2027.64, 306.67]</t>
+          <t>[3459.64, 827.6, 597.78]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[746.07, 2097.7, 364.17]</t>
+          <t>[5168.28, 549.47, 727.18]</t>
         </is>
       </c>
     </row>
@@ -1378,31 +1378,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78.84</v>
+        <v>701.8200000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>62.42</v>
+        <v>526.96</v>
       </c>
       <c r="F27" t="n">
-        <v>7.28</v>
+        <v>35.5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[2109.67, 316.17, 1446.26]</t>
+          <t>[864.12, 631.16, 2078.61]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[2097.7, 364.17, 1573.54]</t>
+          <t>[549.47, 727.18, 3248.83]</t>
         </is>
       </c>
     </row>
@@ -1414,31 +1414,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>455.43</v>
+        <v>798.15</v>
       </c>
       <c r="E28" t="n">
-        <v>317.44</v>
+        <v>626.71</v>
       </c>
       <c r="F28" t="n">
-        <v>17.1</v>
+        <v>34.6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[319.96, 1441.95, 1745.55]</t>
+          <t>[599.79, 1948.88, 525.99]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[364.17, 1573.54, 2522.07]</t>
+          <t>[727.18, 3248.83, 978.78]</t>
         </is>
       </c>
     </row>
@@ -1450,31 +1450,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>526.09</v>
+        <v>774</v>
       </c>
       <c r="E29" t="n">
-        <v>449.92</v>
+        <v>652.8</v>
       </c>
       <c r="F29" t="n">
-        <v>22.74</v>
+        <v>39.7</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[1472.13, 1754.98, 1053.83]</t>
+          <t>[2013.77, 545.47, 497.66]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[1573.54, 2522.07, 1535.1]</t>
+          <t>[3248.83, 978.78, 787.7]</t>
         </is>
       </c>
     </row>
@@ -1486,31 +1486,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>602.36</v>
+        <v>339.79</v>
       </c>
       <c r="E30" t="n">
-        <v>591</v>
+        <v>334.77</v>
       </c>
       <c r="F30" t="n">
-        <v>27.3</v>
+        <v>29.75</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[1774.2, 1065.81, 2007.31]</t>
+          <t>[574.14, 525.42, 1972.1]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[2522.07, 1535.1, 2563.15]</t>
+          <t>[978.78, 787.7, 2309.5]</t>
         </is>
       </c>
     </row>
@@ -1522,31 +1522,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1134.14</v>
+        <v>361.45</v>
       </c>
       <c r="E31" t="n">
-        <v>940.03</v>
+        <v>315.54</v>
       </c>
       <c r="F31" t="n">
-        <v>28.62</v>
+        <v>32.24</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[1077.15, 2037.53, 3331.75]</t>
+          <t>[568.79, 2144.7, 347.87]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[1535.1, 2563.15, 5168.28]</t>
+          <t>[787.7, 2309.5, 910.76]</t>
         </is>
       </c>
     </row>
@@ -1558,31 +1558,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>167.24</v>
+        <v>168.83</v>
       </c>
       <c r="E32" t="n">
-        <v>125.52</v>
+        <v>139.97</v>
       </c>
       <c r="F32" t="n">
-        <v>23.05</v>
+        <v>13.8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[755.95, 902.11, 883.09]</t>
+          <t>[628.88, 1087.95, 794.29]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[484.2, 801.9, 887.7]</t>
+          <t>[683.3, 1181.92, 1065.8]</t>
         </is>
       </c>
     </row>
@@ -1594,31 +1594,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>85.89</v>
+        <v>200.7</v>
       </c>
       <c r="E33" t="n">
-        <v>79.5</v>
+        <v>185.79</v>
       </c>
       <c r="F33" t="n">
-        <v>11.91</v>
+        <v>15.59</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[893.64, 852.69, 661.16]</t>
+          <t>[1097.8, 799.27, 1205.13]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[801.9, 887.7, 549.4]</t>
+          <t>[1181.92, 1065.8, 1411.84]</t>
         </is>
       </c>
     </row>
@@ -1630,31 +1630,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>134.31</v>
+        <v>230.25</v>
       </c>
       <c r="E34" t="n">
-        <v>118.08</v>
+        <v>228.89</v>
       </c>
       <c r="F34" t="n">
-        <v>15.35</v>
+        <v>15.66</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[838.34, 650.83, 1127.65]</t>
+          <t>[804.5, 1211.53, 2940.77]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[887.7, 549.4, 924.2]</t>
+          <t>[1065.8, 1411.84, 2715.72]</t>
         </is>
       </c>
     </row>
@@ -1666,31 +1666,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>136.81</v>
+        <v>265.77</v>
       </c>
       <c r="E35" t="n">
-        <v>119.18</v>
+        <v>259.49</v>
       </c>
       <c r="F35" t="n">
-        <v>15.52</v>
+        <v>26.89</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[652.72, 1132.43, 833.73]</t>
+          <t>[1229.65, 2992.3, 874.9]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[549.4, 924.2, 879.71]</t>
+          <t>[1411.84, 2715.72, 555.2]</t>
         </is>
       </c>
     </row>
@@ -1702,31 +1702,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>117.39</v>
+        <v>248.59</v>
       </c>
       <c r="E36" t="n">
-        <v>87.29000000000001</v>
+        <v>217.74</v>
       </c>
       <c r="F36" t="n">
-        <v>9.890000000000001</v>
+        <v>24.53</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[1119.32, 823.46, 475.66]</t>
+          <t>[2997.89, 876.61, 885.15]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[924.2, 879.71, 486.18]</t>
+          <t>[2715.72, 555.2, 934.8]</t>
         </is>
       </c>
     </row>
@@ -1738,31 +1738,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>55.39</v>
+        <v>191.07</v>
       </c>
       <c r="E37" t="n">
-        <v>50.87</v>
+        <v>142.78</v>
       </c>
       <c r="F37" t="n">
-        <v>7.07</v>
+        <v>23.26</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[807.22, 465.39, 623.98]</t>
+          <t>[877.5, 885.29, 933.79]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[879.71, 486.18, 683.3]</t>
+          <t>[555.2, 934.8, 877.25]</t>
         </is>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>64</v>
+        <v>43.02</v>
       </c>
       <c r="E38" t="n">
-        <v>55.82</v>
+        <v>32.61</v>
       </c>
       <c r="F38" t="n">
-        <v>6.58</v>
+        <v>3.61</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[468.1, 628.69, 1087.17]</t>
+          <t>[863.75, 899.19, 662.66]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[486.18, 683.3, 1181.92]</t>
+          <t>[934.8, 877.25, 667.5]</t>
         </is>
       </c>
     </row>
@@ -1810,31 +1810,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>168.83</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>139.97</v>
+        <v>51.32</v>
       </c>
       <c r="F39" t="n">
-        <v>13.8</v>
+        <v>5.25</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[628.88, 1087.95, 794.29]</t>
+          <t>[906.39, 668.53, 1132.0]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[683.3, 1181.92, 1065.8]</t>
+          <t>[877.25, 667.5, 1008.2]</t>
         </is>
       </c>
     </row>
@@ -1846,31 +1846,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>200.7</v>
+        <v>111.16</v>
       </c>
       <c r="E40" t="n">
-        <v>185.79</v>
+        <v>90.33</v>
       </c>
       <c r="F40" t="n">
-        <v>15.59</v>
+        <v>10.93</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[1097.8, 799.27, 1205.13]</t>
+          <t>[667.53, 1130.33, 869.08]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[1181.92, 1065.8, 1411.84]</t>
+          <t>[667.5, 1008.2, 720.25]</t>
         </is>
       </c>
     </row>
@@ -1882,31 +1882,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>230.25</v>
+        <v>110.88</v>
       </c>
       <c r="E41" t="n">
-        <v>228.89</v>
+        <v>93.09</v>
       </c>
       <c r="F41" t="n">
-        <v>15.66</v>
+        <v>11.52</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[804.5, 1211.53, 2940.77]</t>
+          <t>[1129.76, 868.63, 501.64]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[1065.8, 1411.84, 2715.72]</t>
+          <t>[1008.2, 720.25, 492.3]</t>
         </is>
       </c>
     </row>
@@ -1918,31 +1918,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>230.7</v>
+        <v>647.5</v>
       </c>
       <c r="E42" t="n">
-        <v>220.85</v>
+        <v>596.58</v>
       </c>
       <c r="F42" t="n">
-        <v>31.26</v>
+        <v>29.95</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[468.45, 524.16, 678.76]</t>
+          <t>[1453.03, 1635.9, 1009.26]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[702.95, 819.01, 545.55]</t>
+          <t>[1694.58, 2388.17, 1805.18]</t>
         </is>
       </c>
     </row>
@@ -1954,31 +1954,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>246.48</v>
+        <v>907.9</v>
       </c>
       <c r="E43" t="n">
-        <v>241.16</v>
+        <v>887.28</v>
       </c>
       <c r="F43" t="n">
-        <v>30.92</v>
+        <v>40.75</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[552.34, 715.64, 700.75]</t>
+          <t>[1662.7, 1026.48, 1217.77]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[819.01, 545.55, 987.47]</t>
+          <t>[2388.17, 1805.18, 2375.43]</t>
         </is>
       </c>
     </row>
@@ -1990,31 +1990,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>273.69</v>
+        <v>1059.11</v>
       </c>
       <c r="E44" t="n">
-        <v>270.22</v>
+        <v>1033.15</v>
       </c>
       <c r="F44" t="n">
-        <v>31.88</v>
+        <v>41.9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[773.53, 734.73, 838.03]</t>
+          <t>[1079.89, 1290.13, 1946.71]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[545.55, 987.47, 1167.97]</t>
+          <t>[1805.18, 2375.43, 3235.58]</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>554.23</v>
+        <v>839.22</v>
       </c>
       <c r="E45" t="n">
-        <v>491.37</v>
+        <v>749.3200000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>31.9</v>
+        <v>34.98</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[719.93, 811.68, 1381.9]</t>
+          <t>[1405.28, 2175.21, 476.93]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[987.47, 1167.97, 2232.18]</t>
+          <t>[2375.43, 3235.58, 694.36]</t>
         </is>
       </c>
     </row>
@@ -2062,31 +2062,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>682.77</v>
+        <v>581.61</v>
       </c>
       <c r="E46" t="n">
-        <v>646.39</v>
+        <v>460.44</v>
       </c>
       <c r="F46" t="n">
-        <v>38.48</v>
+        <v>27.22</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[831.79, 1411.86, 785.7]</t>
+          <t>[2274.87, 525.25, 659.13]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[1167.97, 2232.18, 1568.38]</t>
+          <t>[3235.58, 694.36, 910.63]</t>
         </is>
       </c>
     </row>
@@ -2098,31 +2098,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>679.09</v>
+        <v>182.67</v>
       </c>
       <c r="E47" t="n">
-        <v>648.46</v>
+        <v>181.26</v>
       </c>
       <c r="F47" t="n">
-        <v>35.66</v>
+        <v>25.47</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[1423.69, 795.52, 1330.55]</t>
+          <t>[545.17, 712.6, 789.11]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[2232.18, 1568.38, 1694.58]</t>
+          <t>[694.36, 910.63, 592.57]</t>
         </is>
       </c>
     </row>
@@ -2134,31 +2134,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>660.8200000000001</v>
+        <v>175.03</v>
       </c>
       <c r="E48" t="n">
-        <v>624.5</v>
+        <v>156.6</v>
       </c>
       <c r="F48" t="n">
-        <v>33.3</v>
+        <v>21.84</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[842.76, 1370.35, 1564.52]</t>
+          <t>[749.75, 842.72, 982.81]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[1568.38, 1694.58, 2388.17]</t>
+          <t>[910.63, 592.57, 1041.58]</t>
         </is>
       </c>
     </row>
@@ -2170,31 +2170,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>647.5</v>
+        <v>161.7</v>
       </c>
       <c r="E49" t="n">
-        <v>596.58</v>
+        <v>102.02</v>
       </c>
       <c r="F49" t="n">
-        <v>29.95</v>
+        <v>16.54</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[1453.03, 1635.9, 1009.26]</t>
+          <t>[871.71, 1019.14, 1243.84]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[1694.58, 2388.17, 1805.18]</t>
+          <t>[592.57, 1041.58, 1239.36]</t>
         </is>
       </c>
     </row>
@@ -2206,31 +2206,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>907.9</v>
+        <v>205.78</v>
       </c>
       <c r="E50" t="n">
-        <v>887.28</v>
+        <v>138.73</v>
       </c>
       <c r="F50" t="n">
-        <v>40.75</v>
+        <v>6.93</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[1662.7, 1026.48, 1217.77]</t>
+          <t>[998.52, 1219.48, 1994.37]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[2388.17, 1805.18, 2375.43]</t>
+          <t>[1041.58, 1239.36, 2347.63]</t>
         </is>
       </c>
     </row>
@@ -2242,31 +2242,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1059.11</v>
+        <v>255.41</v>
       </c>
       <c r="E51" t="n">
-        <v>1033.15</v>
+        <v>211.61</v>
       </c>
       <c r="F51" t="n">
-        <v>41.9</v>
+        <v>11.37</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[1079.89, 1290.13, 1946.71]</t>
+          <t>[1248.85, 2041.26, 1251.67]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[1805.18, 2375.43, 3235.58]</t>
+          <t>[1239.36, 2347.63, 1570.65]</t>
         </is>
       </c>
     </row>
@@ -2278,19 +2278,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>[0.0, -0.0, -0.0]</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>[0.0, 0.7, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2316,19 +2316,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>[-0.0, -0.0, -0.0]</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>[0.7, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2354,19 +2354,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="E54" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2375,12 +2375,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.7]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -2392,19 +2392,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.96</v>
+        <v>0.23</v>
       </c>
       <c r="E55" t="n">
-        <v>0.73</v>
+        <v>0.13</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[0.0, 0.7, 1.5]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2430,19 +2430,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.96</v>
+        <v>0.23</v>
       </c>
       <c r="E56" t="n">
-        <v>0.73</v>
+        <v>0.13</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2451,12 +2451,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[0.7, 1.5, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2468,19 +2468,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.87</v>
+        <v>0.23</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[1.5, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2544,19 +2544,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2582,19 +2582,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.5]</t>
         </is>
       </c>
     </row>
@@ -2620,19 +2620,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.23</v>
+        <v>1.54</v>
       </c>
       <c r="E61" t="n">
-        <v>0.13</v>
+        <v>1.23</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 1.5, 2.2]</t>
         </is>
       </c>
     </row>
@@ -2658,31 +2658,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="E62" t="n">
-        <v>1.19</v>
+        <v>0.53</v>
       </c>
       <c r="F62" t="n">
-        <v>39.49</v>
+        <v>28.09</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[2.35, 2.08, 3.06]</t>
+          <t>[2.55, 1.93, 2.71]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[3.9, 1.4, 4.4]</t>
+          <t>[1.8, 1.8, 2.0]</t>
         </is>
       </c>
     </row>
@@ -2694,31 +2694,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.99</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>0.93</v>
+        <v>0.49</v>
       </c>
       <c r="F63" t="n">
-        <v>40.64</v>
+        <v>20.75</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[1.83, 3.2, 2.95]</t>
+          <t>[1.89, 2.69, 3.68]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[1.4, 4.4, 1.8]</t>
+          <t>[1.8, 2.0, 3.0]</t>
         </is>
       </c>
     </row>
@@ -2730,31 +2730,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="E64" t="n">
-        <v>0.97</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>39.06</v>
+        <v>44.57</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[3.05, 2.88, 2.28]</t>
+          <t>[2.73, 3.65, 10.71]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[4.4, 1.8, 1.8]</t>
+          <t>[2.0, 3.0, 6.1]</t>
         </is>
       </c>
     </row>
@@ -2766,31 +2766,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.07</v>
+        <v>3.03</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2.61</v>
       </c>
       <c r="F65" t="n">
-        <v>68.53</v>
+        <v>49.83</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[2.88, 2.28, 2.63]</t>
+          <t>[3.66, 10.52, 2.24]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[1.8, 1.8, 1.2]</t>
+          <t>[3.0, 6.1, 5.0]</t>
         </is>
       </c>
     </row>
@@ -2802,31 +2802,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.89</v>
+        <v>3.04</v>
       </c>
       <c r="E66" t="n">
-        <v>0.73</v>
+        <v>2.5</v>
       </c>
       <c r="F66" t="n">
-        <v>56.84</v>
+        <v>48.5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[2.36, 2.63, 1.19]</t>
+          <t>[10.56, 2.22, 1.33]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[1.8, 1.2, 0.99]</t>
+          <t>[6.1, 5.0, 1.6]</t>
         </is>
       </c>
     </row>
@@ -2838,31 +2838,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="E67" t="n">
-        <v>0.87</v>
+        <v>1.21</v>
       </c>
       <c r="F67" t="n">
-        <v>63.77</v>
+        <v>29.48</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[2.58, 1.17, 2.84]</t>
+          <t>[2.24, 1.35, 2.97]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[1.2, 0.99, 1.8]</t>
+          <t>[5.0, 1.6, 3.6]</t>
         </is>
       </c>
     </row>
@@ -2874,31 +2874,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="E68" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="F68" t="n">
-        <v>27.19</v>
+        <v>13.82</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[1.19, 2.85, 1.75]</t>
+          <t>[1.31, 2.98, 2.44]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[0.99, 1.8, 1.8]</t>
+          <t>[1.6, 3.6, 2.3]</t>
         </is>
       </c>
     </row>
@@ -2910,31 +2910,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="E69" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="F69" t="n">
-        <v>28.09</v>
+        <v>12.24</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[2.55, 1.93, 2.71]</t>
+          <t>[2.99, 2.44, 2.05]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[1.8, 1.8, 2.0]</t>
+          <t>[3.6, 2.3, 1.8]</t>
         </is>
       </c>
     </row>
@@ -2946,31 +2946,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="E70" t="n">
-        <v>0.49</v>
+        <v>0.15</v>
       </c>
       <c r="F70" t="n">
-        <v>20.75</v>
+        <v>7.82</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[1.89, 2.69, 3.68]</t>
+          <t>[2.48, 2.07, 1.79]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[1.8, 2.0, 3.0]</t>
+          <t>[2.3, 1.8, 1.8]</t>
         </is>
       </c>
     </row>
@@ -2982,31 +2982,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.72</v>
+        <v>0.39</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>0.32</v>
       </c>
       <c r="F71" t="n">
-        <v>44.57</v>
+        <v>40.1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[2.73, 3.65, 10.71]</t>
+          <t>[2.09, 1.87, 1.2]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[2.0, 3.0, 6.1]</t>
+          <t>[1.8, 1.8, 0.6]</t>
         </is>
       </c>
     </row>
@@ -3018,31 +3018,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>18.33</v>
+        <v>325.82</v>
       </c>
       <c r="E72" t="n">
-        <v>18.2</v>
+        <v>204.95</v>
       </c>
       <c r="F72" t="n">
-        <v>23.14</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[131.17, 112.99, 77.67]</t>
+          <t>[51.62, 43.02, 88.42]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[113.99, 96.8, 56.44]</t>
+          <t>[614.17, 34.8, 44.34]</t>
         </is>
       </c>
     </row>
@@ -3054,31 +3054,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>19.62</v>
+        <v>23.88</v>
       </c>
       <c r="E73" t="n">
-        <v>19.49</v>
+        <v>16.48</v>
       </c>
       <c r="F73" t="n">
-        <v>35.02</v>
+        <v>37.67</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[113.32, 76.59, 63.51]</t>
+          <t>[39.83, 85.25, 58.9]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[96.8, 56.44, 41.7]</t>
+          <t>[34.8, 44.34, 55.41]</t>
         </is>
       </c>
     </row>
@@ -3090,31 +3090,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>19.59</v>
+        <v>27.47</v>
       </c>
       <c r="E74" t="n">
-        <v>19.57</v>
+        <v>22.75</v>
       </c>
       <c r="F74" t="n">
-        <v>42.05</v>
+        <v>43.14</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[75.25, 62.68, 63.38]</t>
+          <t>[85.7, 59.06, 55.37]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[56.44, 41.7, 44.48]</t>
+          <t>[44.34, 55.41, 78.62]</t>
         </is>
       </c>
     </row>
@@ -3126,31 +3126,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>19.8</v>
+        <v>89.13</v>
       </c>
       <c r="E75" t="n">
-        <v>19.75</v>
+        <v>60.14</v>
       </c>
       <c r="F75" t="n">
-        <v>51.85</v>
+        <v>71.8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[63.4, 63.7, 48.73]</t>
+          <t>[60.65, 56.07, 238.73]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[41.7, 44.48, 30.4]</t>
+          <t>[55.41, 78.62, 86.1]</t>
         </is>
       </c>
     </row>
@@ -3162,31 +3162,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>15.82</v>
+        <v>104</v>
       </c>
       <c r="E76" t="n">
-        <v>13.18</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>35.88</v>
+        <v>119.36</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[64.61, 48.96, 62.56]</t>
+          <t>[56.28, 239.27, 152.83]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[44.48, 30.4, 63.4]</t>
+          <t>[78.62, 86.1, 60.7]</t>
         </is>
       </c>
     </row>
@@ -3198,31 +3198,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>325.19</v>
+        <v>104.02</v>
       </c>
       <c r="E77" t="n">
-        <v>194.18</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>51.84</v>
+        <v>135.22</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[49.61, 62.98, 51.25]</t>
+          <t>[236.71, 152.22, 84.22]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[30.4, 63.4, 614.17]</t>
+          <t>[86.1, 60.7, 46.8]</t>
         </is>
       </c>
     </row>
@@ -3234,31 +3234,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>324.88</v>
+        <v>61.85</v>
       </c>
       <c r="E78" t="n">
-        <v>190.43</v>
+        <v>52.34</v>
       </c>
       <c r="F78" t="n">
-        <v>38.57</v>
+        <v>96.67</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[63.91, 51.51, 42.91]</t>
+          <t>[159.11, 82.3, 67.51]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[63.4, 614.17, 34.8]</t>
+          <t>[60.7, 46.8, 44.4]</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>325.82</v>
+        <v>30.2</v>
       </c>
       <c r="E79" t="n">
-        <v>204.95</v>
+        <v>29.66</v>
       </c>
       <c r="F79" t="n">
-        <v>71.54000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[51.62, 43.02, 88.42]</t>
+          <t>[81.27, 66.08, 68.34]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[614.17, 34.8, 44.34]</t>
+          <t>[46.8, 44.4, 35.5]</t>
         </is>
       </c>
     </row>
@@ -3306,31 +3306,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>23.88</v>
+        <v>22.56</v>
       </c>
       <c r="E80" t="n">
-        <v>16.48</v>
+        <v>20.59</v>
       </c>
       <c r="F80" t="n">
-        <v>37.67</v>
+        <v>53.4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[39.83, 85.25, 58.9]</t>
+          <t>[65.13, 67.3, 47.84]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[34.8, 44.34, 55.41]</t>
+          <t>[44.4, 35.5, 38.6]</t>
         </is>
       </c>
     </row>
@@ -3342,31 +3342,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>27.47</v>
+        <v>22.54</v>
       </c>
       <c r="E81" t="n">
-        <v>22.75</v>
+        <v>20.56</v>
       </c>
       <c r="F81" t="n">
-        <v>43.14</v>
+        <v>51.44</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[85.7, 59.06, 55.37]</t>
+          <t>[66.37, 47.08, 71.54]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[44.34, 55.41, 78.62]</t>
+          <t>[35.5, 38.6, 49.2]</t>
         </is>
       </c>
     </row>
@@ -3378,31 +3378,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>74.61</v>
+        <v>190.31</v>
       </c>
       <c r="E82" t="n">
-        <v>73.42</v>
+        <v>181.93</v>
       </c>
       <c r="F82" t="n">
-        <v>5.89</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[1502.67, 965.59, 1601.47]</t>
+          <t>[1574.93, 2047.28, 1284.34]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[1439.06, 901.1, 1509.3]</t>
+          <t>[1742.9, 2303.53, 1405.9]</t>
         </is>
       </c>
     </row>
@@ -3414,31 +3414,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>61.96</v>
+        <v>155.61</v>
       </c>
       <c r="E83" t="n">
-        <v>60.3</v>
+        <v>137.4</v>
       </c>
       <c r="F83" t="n">
-        <v>5.5</v>
+        <v>7.36</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[960.02, 1587.71, 955.85]</t>
+          <t>[2065.94, 1296.8, 1570.59]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[901.1, 1509.3, 912.27]</t>
+          <t>[2303.53, 1405.9, 1636.1]</t>
         </is>
       </c>
     </row>
@@ -3450,31 +3450,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>65.84999999999999</v>
+        <v>110.97</v>
       </c>
       <c r="E84" t="n">
-        <v>60.37</v>
+        <v>102.68</v>
       </c>
       <c r="F84" t="n">
-        <v>4.44</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[1565.04, 942.99, 1416.14]</t>
+          <t>[1305.58, 1583.75, 1185.29]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[1509.3, 912.27, 1510.78]</t>
+          <t>[1405.9, 1636.1, 1029.92]</t>
         </is>
       </c>
     </row>
@@ -3486,31 +3486,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>262</v>
+        <v>98.28</v>
       </c>
       <c r="E85" t="n">
-        <v>190.08</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>10.05</v>
+        <v>6.84</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[939.84, 1409.65, 1719.17]</t>
+          <t>[1590.85, 1191.06, 1438.86]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[912.27, 1510.78, 2160.7]</t>
+          <t>[1636.1, 1029.92, 1469.9]</t>
         </is>
       </c>
     </row>
@@ -3522,31 +3522,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>268.22</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="E86" t="n">
-        <v>194.55</v>
+        <v>71.8</v>
       </c>
       <c r="F86" t="n">
-        <v>10.78</v>
+        <v>6.84</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[1402.85, 1709.5, 542.76]</t>
+          <t>[1192.69, 1443.71, 930.13]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[1510.78, 2160.7, 567.3]</t>
+          <t>[1029.92, 1469.9, 903.7]</t>
         </is>
       </c>
     </row>
@@ -3558,31 +3558,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>277.86</v>
+        <v>31.63</v>
       </c>
       <c r="E87" t="n">
-        <v>219.99</v>
+        <v>29.66</v>
       </c>
       <c r="F87" t="n">
-        <v>11.77</v>
+        <v>2.19</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[1726.65, 548.42, 1535.88]</t>
+          <t>[1429.2, 918.4, 1573.79]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[2160.7, 567.3, 1742.9]</t>
+          <t>[1469.9, 903.7, 1540.2]</t>
         </is>
       </c>
     </row>
@@ -3594,31 +3594,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>175.24</v>
+        <v>25.15</v>
       </c>
       <c r="E88" t="n">
-        <v>142.04</v>
+        <v>22.22</v>
       </c>
       <c r="F88" t="n">
-        <v>7.21</v>
+        <v>1.85</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[561.31, 1576.66, 2049.65]</t>
+          <t>[921.01, 1578.67, 951.35]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[567.3, 1742.9, 2303.53]</t>
+          <t>[903.7, 1540.2, 962.22]</t>
         </is>
       </c>
     </row>
@@ -3630,31 +3630,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>190.31</v>
+        <v>44.12</v>
       </c>
       <c r="E89" t="n">
-        <v>181.93</v>
+        <v>38.27</v>
       </c>
       <c r="F89" t="n">
-        <v>9.800000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[1574.93, 2047.28, 1284.34]</t>
+          <t>[1576.99, 950.06, 1459.44]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[1742.9, 2303.53, 1405.9]</t>
+          <t>[1540.2, 962.22, 1525.3]</t>
         </is>
       </c>
     </row>
@@ -3666,31 +3666,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>155.61</v>
+        <v>199.65</v>
       </c>
       <c r="E90" t="n">
-        <v>137.4</v>
+        <v>139.58</v>
       </c>
       <c r="F90" t="n">
-        <v>7.36</v>
+        <v>7.08</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[2065.94, 1296.8, 1570.59]</t>
+          <t>[949.37, 1458.46, 1843.26]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[2303.53, 1405.9, 1636.1]</t>
+          <t>[962.22, 1525.3, 2182.3]</t>
         </is>
       </c>
     </row>
@@ -3702,31 +3702,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>110.97</v>
+        <v>202.42</v>
       </c>
       <c r="E91" t="n">
-        <v>102.68</v>
+        <v>161.36</v>
       </c>
       <c r="F91" t="n">
-        <v>8.470000000000001</v>
+        <v>10.99</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[1305.58, 1583.75, 1185.29]</t>
+          <t>[1462.45, 1848.7, 559.16]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[1405.9, 1636.1, 1029.92]</t>
+          <t>[1525.3, 2182.3, 646.8]</t>
         </is>
       </c>
     </row>
@@ -3738,31 +3738,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>217.43</v>
+        <v>189.28</v>
       </c>
       <c r="E92" t="n">
-        <v>198.85</v>
+        <v>161.54</v>
       </c>
       <c r="F92" t="n">
-        <v>21.73</v>
+        <v>16.03</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[930.96, 981.39, 1385.59]</t>
+          <t>[533.93, 1087.22, 667.32]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[745.2, 883.08, 1073.09]</t>
+          <t>[609.67, 1386.95, 776.47]</t>
         </is>
       </c>
     </row>
@@ -3774,31 +3774,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>164.27</v>
+        <v>177.4</v>
       </c>
       <c r="E93" t="n">
-        <v>130.16</v>
+        <v>141.72</v>
       </c>
       <c r="F93" t="n">
-        <v>12.78</v>
+        <v>12.07</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[964.2, 1342.94, 1022.42]</t>
+          <t>[1098.2, 678.83, 1341.82]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[883.08, 1073.09, 982.9]</t>
+          <t>[1386.95, 776.47, 1380.59]</t>
         </is>
       </c>
     </row>
@@ -3810,31 +3810,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>150.62</v>
+        <v>263.2</v>
       </c>
       <c r="E94" t="n">
-        <v>118.18</v>
+        <v>182.54</v>
       </c>
       <c r="F94" t="n">
-        <v>11.57</v>
+        <v>8.91</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[1315.17, 999.56, 820.6]</t>
+          <t>[690.7, 1366.24, 2608.94]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[1073.09, 982.9, 916.4]</t>
+          <t>[776.47, 1380.59, 3056.44]</t>
         </is>
       </c>
     </row>
@@ -3846,31 +3846,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>114.42</v>
+        <v>250.17</v>
       </c>
       <c r="E95" t="n">
-        <v>93.23</v>
+        <v>167.15</v>
       </c>
       <c r="F95" t="n">
-        <v>7.57</v>
+        <v>7.61</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[988.44, 808.22, 1770.33]</t>
+          <t>[1374.25, 2628.41, 869.61]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[982.9, 916.4, 1604.36]</t>
+          <t>[1380.59, 3056.44, 802.51]</t>
         </is>
       </c>
     </row>
@@ -3882,31 +3882,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>116.41</v>
+        <v>242.96</v>
       </c>
       <c r="E96" t="n">
-        <v>109.29</v>
+        <v>174.72</v>
       </c>
       <c r="F96" t="n">
-        <v>11.24</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[802.66, 1760.36, 559.78]</t>
+          <t>[2643.74, 874.88, 939.14]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[916.4, 1604.36, 501.65]</t>
+          <t>[3056.44, 802.51, 900.05]</t>
         </is>
       </c>
     </row>
@@ -3918,31 +3918,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>113.29</v>
+        <v>153.39</v>
       </c>
       <c r="E97" t="n">
-        <v>100.52</v>
+        <v>121.44</v>
       </c>
       <c r="F97" t="n">
-        <v>11.33</v>
+        <v>12.59</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[1778.78, 566.13, 547.03]</t>
+          <t>[871.83, 942.05, 1287.47]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[1604.36, 501.65, 609.67]</t>
+          <t>[802.51, 900.05, 1034.46]</t>
         </is>
       </c>
     </row>
@@ -3954,31 +3954,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>175.55</v>
+        <v>144.2</v>
       </c>
       <c r="E98" t="n">
-        <v>139.13</v>
+        <v>104.05</v>
       </c>
       <c r="F98" t="n">
-        <v>14.58</v>
+        <v>10.23</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[557.44, 538.32, 1096.69]</t>
+          <t>[938.39, 1279.59, 1020.92]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[501.65, 609.67, 1386.95]</t>
+          <t>[900.05, 1034.46, 1049.59]</t>
         </is>
       </c>
     </row>
@@ -3990,31 +3990,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>189.28</v>
+        <v>162.45</v>
       </c>
       <c r="E99" t="n">
-        <v>161.54</v>
+        <v>137.43</v>
       </c>
       <c r="F99" t="n">
-        <v>16.03</v>
+        <v>13.42</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[533.93, 1087.22, 667.32]</t>
+          <t>[1277.49, 1018.71, 862.33]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[609.67, 1386.95, 776.47]</t>
+          <t>[1034.46, 1049.59, 1000.72]</t>
         </is>
       </c>
     </row>
@@ -4026,31 +4026,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>177.4</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>141.72</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="F100" t="n">
-        <v>12.07</v>
+        <v>7.88</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[1098.2, 678.83, 1341.82]</t>
+          <t>[1000.87, 846.62, 1721.63]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[1386.95, 776.47, 1380.59]</t>
+          <t>[1049.59, 1000.72, 1661.76]</t>
         </is>
       </c>
     </row>
@@ -4062,31 +4062,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>263.2</v>
+        <v>102.97</v>
       </c>
       <c r="E101" t="n">
-        <v>182.54</v>
+        <v>96.16</v>
       </c>
       <c r="F101" t="n">
-        <v>8.91</v>
+        <v>9.9</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[690.7, 1366.24, 2608.94]</t>
+          <t>[852.57, 1734.61, 574.84]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[776.47, 1380.59, 3056.44]</t>
+          <t>[1000.72, 1661.76, 642.32]</t>
         </is>
       </c>
     </row>
@@ -4098,31 +4098,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>399.77</v>
+        <v>381.51</v>
       </c>
       <c r="E102" t="n">
-        <v>267.47</v>
+        <v>321.81</v>
       </c>
       <c r="F102" t="n">
-        <v>21.41</v>
+        <v>17.4</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[1952.01, 710.2, 1083.74]</t>
+          <t>[1114.23, 2174.68, 901.11]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[1268.71, 717.47, 1195.59]</t>
+          <t>[1277.95, 2785.86, 1091.65]</t>
         </is>
       </c>
     </row>
@@ -4134,31 +4134,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>244.12</v>
+        <v>456.25</v>
       </c>
       <c r="E103" t="n">
-        <v>199.05</v>
+        <v>421.73</v>
       </c>
       <c r="F103" t="n">
-        <v>17.49</v>
+        <v>22.27</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[682.3, 1013.67, 794.89]</t>
+          <t>[2185.9, 906.12, 1217.28]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[717.47, 1195.59, 1174.95]</t>
+          <t>[2785.86, 1091.65, 1696.98]</t>
         </is>
       </c>
     </row>
@@ -4170,31 +4170,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>282</v>
+        <v>794.7</v>
       </c>
       <c r="E104" t="n">
-        <v>270</v>
+        <v>633.3099999999999</v>
       </c>
       <c r="F104" t="n">
-        <v>22.75</v>
+        <v>19.81</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>[1022.61, 802.78, 933.93]</t>
+          <t>[929.44, 1251.51, 5761.64]</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>[1195.59, 1174.95, 1198.78]</t>
+          <t>[1091.65, 1696.98, 7053.88]</t>
         </is>
       </c>
     </row>
@@ -4206,31 +4206,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>577.99</v>
+        <v>813.9400000000001</v>
       </c>
       <c r="E105" t="n">
-        <v>504.62</v>
+        <v>765.42</v>
       </c>
       <c r="F105" t="n">
-        <v>26.1</v>
+        <v>33.55</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[811.5, 946.37, 2514.43]</t>
+          <t>[1297.34, 5984.76, 2163.72]</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[1174.95, 1198.78, 3412.44]</t>
+          <t>[1696.98, 7053.88, 1336.21]</t>
         </is>
       </c>
     </row>
@@ -4242,31 +4242,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>506.38</v>
+        <v>732.5599999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>426.02</v>
+        <v>611.99</v>
       </c>
       <c r="F106" t="n">
-        <v>23.03</v>
+        <v>28.88</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>[972.99, 2599.39, 665.47]</t>
+          <t>[6179.19, 2254.35, 822.44]</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[1198.78, 3412.44, 904.67]</t>
+          <t>[7053.88, 1336.21, 779.29]</t>
         </is>
       </c>
     </row>
@@ -4278,31 +4278,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>488.11</v>
+        <v>583.33</v>
       </c>
       <c r="E107" t="n">
-        <v>412.19</v>
+        <v>385.9</v>
       </c>
       <c r="F107" t="n">
-        <v>21.98</v>
+        <v>30.18</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[2630.55, 674.14, 1053.8]</t>
+          <t>[2340.75, 854.03, 1280.56]</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[3412.44, 904.67, 1277.95]</t>
+          <t>[1336.21, 779.29, 1358.98]</t>
         </is>
       </c>
     </row>
@@ -4314,31 +4314,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>433.99</v>
+        <v>440.82</v>
       </c>
       <c r="E108" t="n">
-        <v>370.38</v>
+        <v>313.74</v>
       </c>
       <c r="F108" t="n">
-        <v>21.58</v>
+        <v>19.83</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[686.62, 1075.03, 2095.7]</t>
+          <t>[789.97, 1167.46, 939.25]</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[904.67, 1277.95, 2785.86]</t>
+          <t>[779.29, 1358.98, 1678.28]</t>
         </is>
       </c>
     </row>
@@ -4350,31 +4350,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>381.51</v>
+        <v>462.67</v>
       </c>
       <c r="E109" t="n">
-        <v>321.81</v>
+        <v>394.1</v>
       </c>
       <c r="F109" t="n">
-        <v>17.4</v>
+        <v>25.75</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>[1114.23, 2174.68, 901.11]</t>
+          <t>[1171.19, 943.94, 1062.15]</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>[1277.95, 2785.86, 1091.65]</t>
+          <t>[1358.98, 1678.28, 1322.31]</t>
         </is>
       </c>
     </row>
@@ -4386,31 +4386,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>456.25</v>
+        <v>637.05</v>
       </c>
       <c r="E110" t="n">
-        <v>421.73</v>
+        <v>585.6</v>
       </c>
       <c r="F110" t="n">
-        <v>22.27</v>
+        <v>27.34</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[2185.9, 906.12, 1217.28]</t>
+          <t>[964.07, 1087.31, 2917.76]</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[2785.86, 1091.65, 1696.98]</t>
+          <t>[1678.28, 1322.31, 3725.33]</t>
         </is>
       </c>
     </row>
@@ -4422,31 +4422,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>794.7</v>
+        <v>391.01</v>
       </c>
       <c r="E111" t="n">
-        <v>633.3099999999999</v>
+        <v>303.98</v>
       </c>
       <c r="F111" t="n">
-        <v>19.81</v>
+        <v>13.57</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[929.44, 1251.51, 5761.64]</t>
+          <t>[1144.25, 3077.61, 787.68]</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[1091.65, 1696.98, 7053.88]</t>
+          <t>[1322.31, 3725.33, 873.84]</t>
         </is>
       </c>
     </row>
@@ -4458,31 +4458,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>97.69</v>
+        <v>52.18</v>
       </c>
       <c r="E112" t="n">
-        <v>56.95</v>
+        <v>46.94</v>
       </c>
       <c r="F112" t="n">
-        <v>10.58</v>
+        <v>13.03</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>[396.29, 268.29, 371.58]</t>
+          <t>[448.19, 449.86, 290.88]</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>[394.91, 268.01, 540.77]</t>
+          <t>[371.41, 407.3, 269.39]</t>
         </is>
       </c>
     </row>
@@ -4494,31 +4494,31 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>99.22</v>
+        <v>25.21</v>
       </c>
       <c r="E113" t="n">
-        <v>64.05</v>
+        <v>23.86</v>
       </c>
       <c r="F113" t="n">
-        <v>13.69</v>
+        <v>7.34</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>[266.52, 370.09, 243.02]</t>
+          <t>[442.1, 284.74, 297.47]</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>[268.01, 540.77, 223.04]</t>
+          <t>[407.3, 269.39, 276.03]</t>
         </is>
       </c>
     </row>
@@ -4530,31 +4530,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>99.89</v>
+        <v>15.7</v>
       </c>
       <c r="E114" t="n">
-        <v>70.03</v>
+        <v>14.43</v>
       </c>
       <c r="F114" t="n">
-        <v>14.1</v>
+        <v>4.78</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>[370.01, 243.71, 1255.74]</t>
+          <t>[284.34, 297.75, 730.02]</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[540.77, 223.04, 1274.39]</t>
+          <t>[269.39, 276.03, 723.39]</t>
         </is>
       </c>
     </row>
@@ -4566,31 +4566,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>73.90000000000001</v>
+        <v>39.09</v>
       </c>
       <c r="E115" t="n">
-        <v>58.75</v>
+        <v>28.31</v>
       </c>
       <c r="F115" t="n">
-        <v>8.02</v>
+        <v>7.89</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>[249.26, 1302.28, 1330.17]</t>
+          <t>[295.21, 724.23, 326.19]</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[223.04, 1274.39, 1208.04]</t>
+          <t>[276.03, 723.39, 391.11]</t>
         </is>
       </c>
     </row>
@@ -4602,31 +4602,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>70.98</v>
+        <v>43.88</v>
       </c>
       <c r="E116" t="n">
-        <v>60.55</v>
+        <v>34.85</v>
       </c>
       <c r="F116" t="n">
-        <v>11.95</v>
+        <v>10.36</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>[1291.11, 1315.35, 282.17]</t>
+          <t>[721.99, 324.46, 227.01]</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[1274.39, 1208.04, 224.55]</t>
+          <t>[723.39, 391.11, 263.5]</t>
         </is>
       </c>
     </row>
@@ -4638,31 +4638,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>83.81999999999999</v>
+        <v>51.08</v>
       </c>
       <c r="E117" t="n">
-        <v>81.67</v>
+        <v>49.39</v>
       </c>
       <c r="F117" t="n">
-        <v>19.04</v>
+        <v>14.39</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>[1308.21, 280.33, 460.47]</t>
+          <t>[323.92, 227.12, 321.81]</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[1208.04, 224.55, 371.41]</t>
+          <t>[391.11, 263.5, 366.41]</t>
         </is>
       </c>
     </row>
@@ -4674,31 +4674,31 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>65.3</v>
+        <v>29.13</v>
       </c>
       <c r="E118" t="n">
-        <v>63.49</v>
+        <v>25.46</v>
       </c>
       <c r="F118" t="n">
-        <v>19.82</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>[278.0, 456.46, 459.28]</t>
+          <t>[230.59, 328.57, 210.77]</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[224.55, 371.41, 407.3]</t>
+          <t>[263.5, 366.41, 216.41]</t>
         </is>
       </c>
     </row>
@@ -4710,31 +4710,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>52.18</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="E119" t="n">
-        <v>46.94</v>
+        <v>54.06</v>
       </c>
       <c r="F119" t="n">
-        <v>13.03</v>
+        <v>6.96</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>[448.19, 449.86, 290.88]</t>
+          <t>[331.98, 213.9, 1088.91]</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>[371.41, 407.3, 269.39]</t>
+          <t>[366.41, 216.41, 1214.16]</t>
         </is>
       </c>
     </row>
@@ -4746,31 +4746,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>25.21</v>
+        <v>81.84</v>
       </c>
       <c r="E120" t="n">
-        <v>23.86</v>
+        <v>66.25</v>
       </c>
       <c r="F120" t="n">
-        <v>7.34</v>
+        <v>5.71</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[442.1, 284.74, 297.47]</t>
+          <t>[215.34, 1098.73, 1072.57]</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>[407.3, 269.39, 276.03]</t>
+          <t>[216.41, 1214.16, 1154.83]</t>
         </is>
       </c>
     </row>
@@ -4782,31 +4782,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>15.7</v>
+        <v>79.02</v>
       </c>
       <c r="E121" t="n">
-        <v>14.43</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F121" t="n">
-        <v>4.78</v>
+        <v>7.86</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[284.34, 297.75, 730.02]</t>
+          <t>[1103.2, 1077.05, 230.79]</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[269.39, 276.03, 723.39]</t>
+          <t>[1214.16, 1154.83, 250.09]</t>
         </is>
       </c>
     </row>
@@ -4818,31 +4818,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>66.19</v>
+        <v>260.1</v>
       </c>
       <c r="E122" t="n">
-        <v>50.95</v>
+        <v>259.7</v>
       </c>
       <c r="F122" t="n">
-        <v>6.9</v>
+        <v>33.76</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>[794.86, 763.94, 832.38]</t>
+          <t>[886.44, 1044.45, 1216.67]</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[779.05, 790.61, 722.0]</t>
+          <t>[624.89, 803.3, 940.25]</t>
         </is>
       </c>
     </row>
@@ -4854,31 +4854,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>111.86</v>
+        <v>230.33</v>
       </c>
       <c r="E123" t="n">
-        <v>97.67</v>
+        <v>229.84</v>
       </c>
       <c r="F123" t="n">
-        <v>13.37</v>
+        <v>26.5</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[765.91, 834.54, 883.29]</t>
+          <t>[1012.28, 1176.35, 1106.04]</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[790.61, 722.0, 727.52]</t>
+          <t>[803.3, 940.25, 861.61]</t>
         </is>
       </c>
     </row>
@@ -4890,31 +4890,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>151.6</v>
+        <v>179.68</v>
       </c>
       <c r="E124" t="n">
-        <v>150.23</v>
+        <v>153.07</v>
       </c>
       <c r="F124" t="n">
-        <v>21.18</v>
+        <v>16.74</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[843.46, 893.0, 846.76]</t>
+          <t>[1156.93, 1084.11, 1508.32]</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[722.0, 727.52, 683.02]</t>
+          <t>[940.25, 861.61, 1488.29]</t>
         </is>
       </c>
     </row>
@@ -4926,31 +4926,31 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>230.36</v>
+        <v>133.91</v>
       </c>
       <c r="E125" t="n">
-        <v>213.71</v>
+        <v>105.26</v>
       </c>
       <c r="F125" t="n">
-        <v>24.27</v>
+        <v>12.27</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>[882.11, 834.27, 804.69]</t>
+          <t>[1071.85, 1480.37, 919.14]</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[727.52, 683.02, 1139.98]</t>
+          <t>[861.61, 1488.29, 821.5]</t>
         </is>
       </c>
     </row>
@@ -4962,31 +4962,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>240.17</v>
+        <v>50.16</v>
       </c>
       <c r="E126" t="n">
-        <v>222.22</v>
+        <v>36.49</v>
       </c>
       <c r="F126" t="n">
-        <v>22.67</v>
+        <v>3.99</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>[821.57, 791.07, 867.21]</t>
+          <t>[1463.24, 904.68, 820.31]</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>[683.02, 1139.98, 1046.42]</t>
+          <t>[1488.29, 821.5, 819.07]</t>
         </is>
       </c>
     </row>
@@ -4998,31 +4998,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>268.37</v>
+        <v>74.62</v>
       </c>
       <c r="E127" t="n">
-        <v>257.71</v>
+        <v>61.37</v>
       </c>
       <c r="F127" t="n">
-        <v>28.28</v>
+        <v>7.8</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>[776.86, 850.4, 838.88]</t>
+          <t>[904.99, 821.07, 857.29]</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[1139.98, 1046.42, 624.89]</t>
+          <t>[821.5, 819.07, 758.66]</t>
         </is>
       </c>
     </row>
@@ -5034,31 +5034,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>212.28</v>
+        <v>53.4</v>
       </c>
       <c r="E128" t="n">
-        <v>210.44</v>
+        <v>31.57</v>
       </c>
       <c r="F128" t="n">
-        <v>27.38</v>
+        <v>4.15</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[872.91, 865.75, 1020.24]</t>
+          <t>[816.92, 851.13, 872.41]</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>[1046.42, 624.89, 803.3]</t>
+          <t>[819.07, 758.66, 872.49]</t>
         </is>
       </c>
     </row>
@@ -5070,31 +5070,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>260.1</v>
+        <v>159.93</v>
       </c>
       <c r="E129" t="n">
-        <v>259.7</v>
+        <v>118.42</v>
       </c>
       <c r="F129" t="n">
-        <v>33.76</v>
+        <v>19.17</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[886.44, 1044.45, 1216.67]</t>
+          <t>[852.19, 873.49, 839.46]</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>[624.89, 803.3, 940.25]</t>
+          <t>[758.66, 872.49, 578.73]</t>
         </is>
       </c>
     </row>
@@ -5106,31 +5106,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>230.33</v>
+        <v>233.35</v>
       </c>
       <c r="E130" t="n">
-        <v>229.84</v>
+        <v>191.83</v>
       </c>
       <c r="F130" t="n">
-        <v>26.5</v>
+        <v>23.64</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>[1012.28, 1176.35, 1106.04]</t>
+          <t>[864.89, 830.63, 874.95]</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>[803.3, 940.25, 861.61]</t>
+          <t>[872.49, 578.73, 1190.92]</t>
         </is>
       </c>
     </row>
@@ -5142,31 +5142,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>179.68</v>
+        <v>248.44</v>
       </c>
       <c r="E131" t="n">
-        <v>153.07</v>
+        <v>238.36</v>
       </c>
       <c r="F131" t="n">
-        <v>16.74</v>
+        <v>27.89</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>[1156.93, 1084.11, 1508.32]</t>
+          <t>[829.14, 873.43, 923.48]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[940.25, 861.61, 1488.29]</t>
+          <t>[578.73, 1190.92, 1070.66]</t>
         </is>
       </c>
     </row>
@@ -5178,31 +5178,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>23.46</v>
+        <v>118.54</v>
       </c>
       <c r="E132" t="n">
-        <v>16.46</v>
+        <v>74.16</v>
       </c>
       <c r="F132" t="n">
-        <v>19.97</v>
+        <v>15.91</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[138.55, 137.45, 49.98]</t>
+          <t>[128.88, 370.34, 234.21]</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[98.7, 135.6, 42.3]</t>
+          <t>[146.4, 574.9, 234.6]</t>
         </is>
       </c>
     </row>
@@ -5214,31 +5214,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5.39</v>
+        <v>124.52</v>
       </c>
       <c r="E133" t="n">
-        <v>5.08</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>7.7</v>
+        <v>18.79</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[138.45, 49.54, 138.65]</t>
+          <t>[367.69, 237.32, 251.85]</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>[135.6, 42.3, 133.5]</t>
+          <t>[574.9, 234.6, 311.6]</t>
         </is>
       </c>
     </row>
@@ -5250,31 +5250,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.62</v>
+        <v>42.64</v>
       </c>
       <c r="E134" t="n">
-        <v>10.88</v>
+        <v>37.43</v>
       </c>
       <c r="F134" t="n">
-        <v>13.31</v>
+        <v>9.75</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>[48.2, 144.32, 105.02]</t>
+          <t>[225.93, 257.51, 554.06]</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>[42.3, 133.5, 89.1]</t>
+          <t>[234.6, 311.6, 603.6]</t>
         </is>
       </c>
     </row>
@@ -5286,31 +5286,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>28.4</v>
+        <v>51.51</v>
       </c>
       <c r="E135" t="n">
-        <v>21.54</v>
+        <v>50.8</v>
       </c>
       <c r="F135" t="n">
-        <v>11.71</v>
+        <v>23.62</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[133.06, 107.79, 283.3]</t>
+          <t>[252.76, 549.06, 129.94]</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>[133.5, 89.1, 328.8]</t>
+          <t>[311.6, 603.6, 90.9]</t>
         </is>
       </c>
     </row>
@@ -5322,31 +5322,31 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>29.51</v>
+        <v>41.21</v>
       </c>
       <c r="E136" t="n">
-        <v>23.21</v>
+        <v>41.05</v>
       </c>
       <c r="F136" t="n">
-        <v>12.29</v>
+        <v>27.53</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[106.87, 281.06, 166.87]</t>
+          <t>[558.43, 132.43, 160.4]</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>[89.1, 328.8, 171.0]</t>
+          <t>[603.6, 90.9, 123.95]</t>
         </is>
       </c>
     </row>
@@ -5358,31 +5358,31 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>43.72</v>
+        <v>93.06</v>
       </c>
       <c r="E137" t="n">
-        <v>34.86</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="F137" t="n">
-        <v>14.27</v>
+        <v>48.39</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>[256.75, 184.58, 127.44]</t>
+          <t>[130.91, 157.09, 52.46]</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>[328.8, 171.0, 146.4]</t>
+          <t>[90.9, 123.95, 205.05]</t>
         </is>
       </c>
     </row>
@@ -5394,31 +5394,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>119.86</v>
+        <v>90.62</v>
       </c>
       <c r="E138" t="n">
-        <v>73.98</v>
+        <v>62.79</v>
       </c>
       <c r="F138" t="n">
-        <v>15.33</v>
+        <v>34.38</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>[172.31, 132.94, 367.73]</t>
+          <t>[159.11, 52.08, 131.35]</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>[171.0, 146.4, 574.9]</t>
+          <t>[123.95, 205.05, 131.6]</t>
         </is>
       </c>
     </row>
@@ -5430,31 +5430,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>118.54</v>
+        <v>101.41</v>
       </c>
       <c r="E139" t="n">
-        <v>74.16</v>
+        <v>79.84</v>
       </c>
       <c r="F139" t="n">
-        <v>15.91</v>
+        <v>39.78</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>[128.88, 370.34, 234.21]</t>
+          <t>[52.02, 131.33, 107.48]</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>[146.4, 574.9, 234.6]</t>
+          <t>[205.05, 131.6, 193.7]</t>
         </is>
       </c>
     </row>
@@ -5466,31 +5466,31 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>124.52</v>
+        <v>47.93</v>
       </c>
       <c r="E140" t="n">
-        <v>89.90000000000001</v>
+        <v>31.88</v>
       </c>
       <c r="F140" t="n">
-        <v>18.79</v>
+        <v>16.06</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>[367.69, 237.32, 251.85]</t>
+          <t>[134.66, 111.38, 316.05]</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>[574.9, 234.6, 311.6]</t>
+          <t>[131.6, 193.7, 305.8]</t>
         </is>
       </c>
     </row>
@@ -5502,31 +5502,31 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>42.64</v>
+        <v>48.31</v>
       </c>
       <c r="E141" t="n">
-        <v>37.43</v>
+        <v>32.17</v>
       </c>
       <c r="F141" t="n">
-        <v>9.75</v>
+        <v>16.4</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>[225.93, 257.51, 554.06]</t>
+          <t>[110.56, 312.85, 165.93]</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>[234.6, 311.6, 603.6]</t>
+          <t>[193.7, 305.8, 159.6]</t>
         </is>
       </c>
     </row>
@@ -5538,31 +5538,31 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3093.31</v>
+        <v>1592.34</v>
       </c>
       <c r="E142" t="n">
-        <v>3070.86</v>
+        <v>1494.34</v>
       </c>
       <c r="F142" t="n">
-        <v>196.42</v>
+        <v>27.78</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>[4704.91, 4833.83, 4957.63]</t>
+          <t>[6672.97, 8635.89, 2889.64]</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>[1145.33, 1838.78, 2299.68]</t>
+          <t>[5536.26, 6364.54, 3964.6]</t>
         </is>
       </c>
     </row>
@@ -5574,31 +5574,31 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1460.47</v>
+        <v>1139.07</v>
       </c>
       <c r="E143" t="n">
-        <v>1434.56</v>
+        <v>1083.31</v>
       </c>
       <c r="F143" t="n">
-        <v>67.34</v>
+        <v>28.17</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[3639.37, 3660.87, 3683.98]</t>
+          <t>[6993.16, 2478.37, 4190.85]</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[1838.78, 2299.68, 2542.07]</t>
+          <t>[6364.54, 3964.6, 3055.77]</t>
         </is>
       </c>
     </row>
@@ -5610,31 +5610,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>655.01</v>
+        <v>1825.71</v>
       </c>
       <c r="E144" t="n">
-        <v>554.9</v>
+        <v>1490.34</v>
       </c>
       <c r="F144" t="n">
-        <v>22.89</v>
+        <v>29.69</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>[3215.18, 3206.77, 3198.66]</t>
+          <t>[1798.71, 3056.88, 4395.49]</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[2299.68, 2542.07, 3114.16]</t>
+          <t>[3964.6, 3055.77, 6699.51]</t>
         </is>
       </c>
     </row>
@@ -5646,31 +5646,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2302.05</v>
+        <v>1554.13</v>
       </c>
       <c r="E145" t="n">
-        <v>1515.33</v>
+        <v>1370.85</v>
       </c>
       <c r="F145" t="n">
-        <v>26.47</v>
+        <v>52.05</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[3035.87, 3017.36, 2998.36]</t>
+          <t>[5452.34, 7680.2, 1900.81]</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[2542.07, 3114.16, 6953.75]</t>
+          <t>[3055.77, 6699.51, 1165.51]</t>
         </is>
       </c>
     </row>
@@ -5682,31 +5682,31 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2404.74</v>
+        <v>578.6</v>
       </c>
       <c r="E146" t="n">
-        <v>1707.16</v>
+        <v>517.11</v>
       </c>
       <c r="F146" t="n">
-        <v>29.33</v>
+        <v>20.36</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>[2904.63, 2879.0, 2854.42]</t>
+          <t>[5815.34, 1499.02, 2066.57]</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[3114.16, 6953.75, 3691.63]</t>
+          <t>[6699.51, 1165.51, 1732.91]</t>
         </is>
       </c>
     </row>
@@ -5718,31 +5718,31 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2820.91</v>
+        <v>345.87</v>
       </c>
       <c r="E147" t="n">
-        <v>2488.76</v>
+        <v>319.4</v>
       </c>
       <c r="F147" t="n">
-        <v>42.38</v>
+        <v>21.53</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[2926.99, 2905.31, 2883.07]</t>
+          <t>[1567.19, 2157.23, 2479.72]</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>[6953.75, 3691.63, 5536.26]</t>
+          <t>[1165.51, 1732.91, 2347.51]</t>
         </is>
       </c>
     </row>
@@ -5754,31 +5754,31 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1731.66</v>
+        <v>170.26</v>
       </c>
       <c r="E148" t="n">
-        <v>1290.23</v>
+        <v>156.61</v>
       </c>
       <c r="F148" t="n">
-        <v>21.59</v>
+        <v>7.79</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>[3511.71, 6344.18, 9247.4]</t>
+          <t>[1984.0, 2238.4, 2474.09]</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>[3691.63, 5536.26, 6364.54]</t>
+          <t>[1732.91, 2347.51, 2583.73]</t>
         </is>
       </c>
     </row>
@@ -5790,31 +5790,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1592.34</v>
+        <v>249.29</v>
       </c>
       <c r="E149" t="n">
-        <v>1494.34</v>
+        <v>248.19</v>
       </c>
       <c r="F149" t="n">
-        <v>27.78</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>[6672.97, 8635.89, 2889.64]</t>
+          <t>[2127.91, 2335.68, 2903.16]</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[5536.26, 6364.54, 3964.6]</t>
+          <t>[2347.51, 2583.73, 3180.08]</t>
         </is>
       </c>
     </row>
@@ -5826,31 +5826,31 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1139.07</v>
+        <v>498.7</v>
       </c>
       <c r="E150" t="n">
-        <v>1083.31</v>
+        <v>361.81</v>
       </c>
       <c r="F150" t="n">
-        <v>28.17</v>
+        <v>7.67</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[6993.16, 2478.37, 4190.85]</t>
+          <t>[2456.56, 3068.91, 6652.79]</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[6364.54, 3964.6, 3055.77]</t>
+          <t>[2583.73, 3180.08, 5805.7]</t>
         </is>
       </c>
     </row>
@@ -5862,31 +5862,31 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1825.71</v>
+        <v>1578.99</v>
       </c>
       <c r="E151" t="n">
-        <v>1490.34</v>
+        <v>1187.96</v>
       </c>
       <c r="F151" t="n">
-        <v>29.69</v>
+        <v>20.15</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[1798.71, 3056.88, 4395.49]</t>
+          <t>[3106.76, 6719.63, 3500.68]</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[3964.6, 3055.77, 6699.51]</t>
+          <t>[3180.08, 5805.7, 6077.3]</t>
         </is>
       </c>
     </row>
@@ -5898,31 +5898,31 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>161.42</v>
+        <v>240.07</v>
       </c>
       <c r="E152" t="n">
-        <v>135.28</v>
+        <v>189.8</v>
       </c>
       <c r="F152" t="n">
-        <v>11.92</v>
+        <v>12.55</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[1258.67, 1271.85, 1284.3]</t>
+          <t>[1977.02, 1909.77, 1051.74]</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>[1226.1, 1024.19, 1409.9]</t>
+          <t>[1580.6, 1976.4, 1158.11]</t>
         </is>
       </c>
     </row>
@@ -5934,31 +5934,31 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>558.83</v>
+        <v>306.65</v>
       </c>
       <c r="E153" t="n">
-        <v>433.91</v>
+        <v>292.87</v>
       </c>
       <c r="F153" t="n">
-        <v>96.36</v>
+        <v>19</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[1265.44, 1277.39, 1290.28]</t>
+          <t>[1558.48, 953.58, 1150.73]</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[1024.19, 1409.9, 362.31]</t>
+          <t>[1976.4, 1158.11, 1406.9]</t>
         </is>
       </c>
     </row>
@@ -5970,31 +5970,31 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>737.67</v>
+        <v>425.49</v>
       </c>
       <c r="E154" t="n">
-        <v>660.98</v>
+        <v>357.39</v>
       </c>
       <c r="F154" t="n">
-        <v>186.99</v>
+        <v>18.02</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>[1210.25, 1218.22, 1225.98]</t>
+          <t>[1077.41, 1061.34, 2221.88]</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[1409.9, 362.31, 298.6]</t>
+          <t>[1158.11, 1406.9, 2867.79]</t>
         </is>
       </c>
     </row>
@@ -6006,31 +6006,31 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1290.77</v>
+        <v>325.32</v>
       </c>
       <c r="E155" t="n">
-        <v>1230.76</v>
+        <v>243.53</v>
       </c>
       <c r="F155" t="n">
-        <v>214.76</v>
+        <v>10.9</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[1281.06, 1292.97, 1305.39]</t>
+          <t>[1249.3, 2327.81, 1204.31]</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>[362.31, 298.6, 3084.55]</t>
+          <t>[1406.9, 2867.79, 1237.31]</t>
         </is>
       </c>
     </row>
@@ -6042,31 +6042,31 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1344.13</v>
+        <v>177.55</v>
       </c>
       <c r="E156" t="n">
-        <v>1191.7</v>
+        <v>153.38</v>
       </c>
       <c r="F156" t="n">
-        <v>218.78</v>
+        <v>12.34</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[1019.8, 1014.36, 1009.12]</t>
+          <t>[2919.68, 1506.83, 893.71]</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[298.6, 3084.55, 225.4]</t>
+          <t>[2867.79, 1237.31, 1032.43]</t>
         </is>
       </c>
     </row>
@@ -6078,31 +6078,31 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1418.1</v>
+        <v>86.67</v>
       </c>
       <c r="E157" t="n">
-        <v>1207.6</v>
+        <v>67.64</v>
       </c>
       <c r="F157" t="n">
-        <v>128.26</v>
+        <v>5.26</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>[831.04, 817.17, 803.08]</t>
+          <t>[1376.1, 1039.83, 1526.98]</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[3084.55, 225.4, 1580.6]</t>
+          <t>[1237.31, 1032.43, 1470.26]</t>
         </is>
       </c>
     </row>
@@ -6114,31 +6114,31 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>282.16</v>
+        <v>201</v>
       </c>
       <c r="E158" t="n">
-        <v>237.85</v>
+        <v>180.95</v>
       </c>
       <c r="F158" t="n">
-        <v>16.64</v>
+        <v>19.42</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>[201.77, 1937.64, 2309.28]</t>
+          <t>[749.58, 1279.46, 317.5]</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[225.4, 1580.6, 1976.4]</t>
+          <t>[1032.43, 1470.26, 386.71]</t>
         </is>
       </c>
     </row>
@@ -6150,31 +6150,31 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>240.07</v>
+        <v>47.68</v>
       </c>
       <c r="E159" t="n">
-        <v>189.8</v>
+        <v>44.57</v>
       </c>
       <c r="F159" t="n">
-        <v>12.55</v>
+        <v>7.89</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[1977.02, 1909.77, 1051.74]</t>
+          <t>[1410.26, 365.71, 319.3]</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[1580.6, 1976.4, 1158.11]</t>
+          <t>[1470.26, 386.71, 372.01]</t>
         </is>
       </c>
     </row>
@@ -6186,31 +6186,31 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>306.65</v>
+        <v>69.75</v>
       </c>
       <c r="E160" t="n">
-        <v>292.87</v>
+        <v>53.06</v>
       </c>
       <c r="F160" t="n">
-        <v>19</v>
+        <v>5.17</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[1558.48, 953.58, 1150.73]</t>
+          <t>[379.67, 334.52, 3294.98]</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[1976.4, 1158.11, 1406.9]</t>
+          <t>[386.71, 372.01, 3180.35]</t>
         </is>
       </c>
     </row>
@@ -6222,31 +6222,31 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>425.49</v>
+        <v>78.12</v>
       </c>
       <c r="E161" t="n">
-        <v>357.39</v>
+        <v>62.07</v>
       </c>
       <c r="F161" t="n">
-        <v>18.02</v>
+        <v>7.3</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[1077.41, 1061.34, 2221.88]</t>
+          <t>[336.32, 3309.03, 242.72]</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[1158.11, 1406.9, 2867.79]</t>
+          <t>[372.01, 3180.35, 264.57]</t>
         </is>
       </c>
     </row>
@@ -6258,31 +6258,31 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>755.4400000000001</v>
+        <v>218.29</v>
       </c>
       <c r="E162" t="n">
-        <v>721.8</v>
+        <v>206.1</v>
       </c>
       <c r="F162" t="n">
-        <v>95.97</v>
+        <v>23.82</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[1173.18, 1197.52, 1220.75]</t>
+          <t>[1090.3, 1880.72, 968.97]</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[2131.2, 413.0, 797.9]</t>
+          <t>[944.9, 1715.0, 661.8]</t>
         </is>
       </c>
     </row>
@@ -6294,31 +6294,31 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>873.6900000000001</v>
+        <v>208.24</v>
       </c>
       <c r="E163" t="n">
-        <v>851.04</v>
+        <v>189.86</v>
       </c>
       <c r="F163" t="n">
-        <v>192.58</v>
+        <v>22.61</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[1341.11, 1377.73, 1417.98]</t>
+          <t>[1876.73, 967.61, 734.55]</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>[413.0, 797.9, 372.8]</t>
+          <t>[1715.0, 661.8, 836.6]</t>
         </is>
       </c>
     </row>
@@ -6330,31 +6330,31 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>618.62</v>
+        <v>573.6900000000001</v>
       </c>
       <c r="E164" t="n">
-        <v>585.0700000000001</v>
+        <v>449.73</v>
       </c>
       <c r="F164" t="n">
-        <v>136.1</v>
+        <v>27.9</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[1099.25, 1113.73, 1127.94]</t>
+          <t>[989.84, 749.34, 3005.11]</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[797.9, 372.8, 415.0]</t>
+          <t>[661.8, 836.6, 3939.0]</t>
         </is>
       </c>
     </row>
@@ -6366,31 +6366,31 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>599.1</v>
+        <v>523.88</v>
       </c>
       <c r="E165" t="n">
-        <v>591</v>
+        <v>422.18</v>
       </c>
       <c r="F165" t="n">
-        <v>122.07</v>
+        <v>15.03</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[1049.04, 1058.29, 1067.94]</t>
+          <t>[798.31, 3141.09, 2556.36]</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>[372.8, 415.0, 1521.4]</t>
+          <t>[836.6, 3939.0, 2126.0]</t>
         </is>
       </c>
     </row>
@@ -6402,31 +6402,31 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>466.13</v>
+        <v>521.86</v>
       </c>
       <c r="E166" t="n">
-        <v>421.22</v>
+        <v>415.41</v>
       </c>
       <c r="F166" t="n">
-        <v>59.01</v>
+        <v>16.66</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>[888.07, 885.78, 883.57]</t>
+          <t>[3120.89, 2507.48, 460.13]</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>[415.0, 1521.4, 728.6]</t>
+          <t>[3939.0, 2126.0, 413.5]</t>
         </is>
       </c>
     </row>
@@ -6438,31 +6438,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>445.75</v>
+        <v>142.77</v>
       </c>
       <c r="E167" t="n">
-        <v>324.08</v>
+        <v>95.52</v>
       </c>
       <c r="F167" t="n">
-        <v>24.69</v>
+        <v>6.59</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>[773.27, 765.63, 757.82]</t>
+          <t>[2371.43, 439.78, 810.16]</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>[1521.4, 728.6, 944.9]</t>
+          <t>[2126.0, 413.5, 795.3]</t>
         </is>
       </c>
     </row>
@@ -6474,31 +6474,31 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>320.93</v>
+        <v>28.27</v>
       </c>
       <c r="E168" t="n">
-        <v>275.06</v>
+        <v>18.36</v>
       </c>
       <c r="F168" t="n">
-        <v>30.95</v>
+        <v>4.19</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[227.82, 835.56, 1499.93]</t>
+          <t>[462.03, 801.78, 373.54]</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>[728.6, 944.9, 1715.0]</t>
+          <t>[413.5, 795.3, 373.6]</t>
         </is>
       </c>
     </row>
@@ -6510,31 +6510,31 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>218.29</v>
+        <v>3.3</v>
       </c>
       <c r="E169" t="n">
-        <v>206.1</v>
+        <v>2.8</v>
       </c>
       <c r="F169" t="n">
-        <v>23.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[1090.3, 1880.72, 968.97]</t>
+          <t>[794.88, 370.27, 411.16]</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>[944.9, 1715.0, 661.8]</t>
+          <t>[795.3, 373.6, 415.8]</t>
         </is>
       </c>
     </row>
@@ -6546,31 +6546,31 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>208.24</v>
+        <v>34.61</v>
       </c>
       <c r="E170" t="n">
-        <v>189.86</v>
+        <v>22.11</v>
       </c>
       <c r="F170" t="n">
-        <v>22.61</v>
+        <v>1.87</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[1876.73, 967.61, 734.55]</t>
+          <t>[370.78, 412.07, 1573.47]</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>[1715.0, 661.8, 836.6]</t>
+          <t>[373.6, 415.8, 1513.7]</t>
         </is>
       </c>
     </row>
@@ -6582,31 +6582,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>573.6900000000001</v>
+        <v>59.6</v>
       </c>
       <c r="E171" t="n">
-        <v>449.73</v>
+        <v>48.68</v>
       </c>
       <c r="F171" t="n">
-        <v>27.9</v>
+        <v>5.4</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[989.84, 749.34, 3005.11]</t>
+          <t>[411.89, 1568.32, 664.18]</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>[661.8, 836.6, 3939.0]</t>
+          <t>[415.8, 1513.7, 751.7]</t>
         </is>
       </c>
     </row>
@@ -6618,31 +6618,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>877.9</v>
+        <v>446.1</v>
       </c>
       <c r="E172" t="n">
-        <v>700.58</v>
+        <v>372.45</v>
       </c>
       <c r="F172" t="n">
-        <v>48.28</v>
+        <v>15.87</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[2915.54, 1758.12, 1763.69]</t>
+          <t>[2847.74, 2900.65, 3177.17]</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[1473.51, 1514.97, 1347.13]</t>
+          <t>[2132.52, 2747.67, 2928.02]</t>
         </is>
       </c>
     </row>
@@ -6654,31 +6654,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>273.83</v>
+        <v>459.13</v>
       </c>
       <c r="E173" t="n">
-        <v>250.28</v>
+        <v>357.36</v>
       </c>
       <c r="F173" t="n">
-        <v>15.86</v>
+        <v>12.64</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[1639.44, 1578.86, 1385.63]</t>
+          <t>[2856.26, 3130.1, 3573.36]</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>[1514.97, 1347.13, 1780.28]</t>
+          <t>[2747.67, 2928.02, 2811.94]</t>
         </is>
       </c>
     </row>
@@ -6690,31 +6690,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>279.08</v>
+        <v>450.07</v>
       </c>
       <c r="E174" t="n">
-        <v>254.89</v>
+        <v>369.47</v>
       </c>
       <c r="F174" t="n">
-        <v>15.29</v>
+        <v>12.16</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[1548.85, 1367.45, 1800.76]</t>
+          <t>[3110.34, 3544.82, 4808.36]</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>[1347.13, 1780.28, 1950.87]</t>
+          <t>[2928.02, 2811.94, 4615.15]</t>
         </is>
       </c>
     </row>
@@ -6726,31 +6726,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1015.25</v>
+        <v>1132.17</v>
       </c>
       <c r="E175" t="n">
-        <v>759.6900000000001</v>
+        <v>915.79</v>
       </c>
       <c r="F175" t="n">
-        <v>22.43</v>
+        <v>47.1</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[1364.9, 1788.11, 3075.41]</t>
+          <t>[3562.08, 4811.21, 3432.97]</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>[1780.28, 1950.87, 4776.34]</t>
+          <t>[2811.94, 4615.15, 1631.78]</t>
         </is>
       </c>
     </row>
@@ -6762,31 +6762,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1011.41</v>
+        <v>1050.87</v>
       </c>
       <c r="E176" t="n">
-        <v>785.89</v>
+        <v>801.27</v>
       </c>
       <c r="F176" t="n">
-        <v>21.44</v>
+        <v>47.57</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>[1805.85, 3122.33, 1949.87]</t>
+          <t>[4764.69, 3371.2, 2080.42]</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>[1950.87, 4776.34, 2508.52]</t>
+          <t>[4615.15, 1631.78, 1565.58]</t>
         </is>
       </c>
     </row>
@@ -6798,31 +6798,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1062.65</v>
+        <v>1026.18</v>
       </c>
       <c r="E177" t="n">
-        <v>933.24</v>
+        <v>744.29</v>
       </c>
       <c r="F177" t="n">
-        <v>28.17</v>
+        <v>46.01</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[3124.61, 1951.28, 2723.26]</t>
+          <t>[3334.13, 2076.2, 1824.65]</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[4776.34, 2508.52, 2132.52]</t>
+          <t>[1631.78, 1565.58, 1804.74]</t>
         </is>
       </c>
     </row>
@@ -6834,31 +6834,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>489.06</v>
+        <v>276.77</v>
       </c>
       <c r="E178" t="n">
-        <v>425.73</v>
+        <v>234.58</v>
       </c>
       <c r="F178" t="n">
-        <v>18.44</v>
+        <v>14.86</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[2010.16, 2809.93, 2849.1]</t>
+          <t>[1996.02, 1727.99, 1729.75]</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>[2508.52, 2132.52, 2747.67]</t>
+          <t>[1565.58, 1804.74, 1533.22]</t>
         </is>
       </c>
     </row>
@@ -6870,31 +6870,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>446.1</v>
+        <v>242.69</v>
       </c>
       <c r="E179" t="n">
-        <v>372.45</v>
+        <v>213.21</v>
       </c>
       <c r="F179" t="n">
-        <v>15.87</v>
+        <v>13.29</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[2847.74, 2900.65, 3177.17]</t>
+          <t>[1703.72, 1698.99, 1962.14]</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[2132.52, 2747.67, 2928.02]</t>
+          <t>[1804.74, 1533.22, 1589.3]</t>
         </is>
       </c>
     </row>
@@ -6906,31 +6906,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>459.13</v>
+        <v>245.96</v>
       </c>
       <c r="E180" t="n">
-        <v>357.36</v>
+        <v>209.9</v>
       </c>
       <c r="F180" t="n">
-        <v>12.64</v>
+        <v>12.52</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[2856.26, 3130.1, 3573.36]</t>
+          <t>[1705.81, 1971.52, 3407.48]</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>[2747.67, 2928.02, 2811.94]</t>
+          <t>[1533.22, 1589.3, 3332.59]</t>
         </is>
       </c>
     </row>
@@ -6942,31 +6942,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>450.07</v>
+        <v>272.4</v>
       </c>
       <c r="E181" t="n">
-        <v>369.47</v>
+        <v>237.75</v>
       </c>
       <c r="F181" t="n">
-        <v>12.16</v>
+        <v>12.4</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[3110.34, 3544.82, 4808.36]</t>
+          <t>[1951.34, 3386.01, 2028.02]</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[2928.02, 2811.94, 4615.15]</t>
+          <t>[1589.3, 3332.59, 2325.81]</t>
         </is>
       </c>
     </row>
@@ -6978,31 +6978,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>73.86</v>
+        <v>76.03</v>
       </c>
       <c r="E182" t="n">
-        <v>63.47</v>
+        <v>67.13</v>
       </c>
       <c r="F182" t="n">
-        <v>12.01</v>
+        <v>4.55</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[917.71, 306.14, 366.23]</t>
+          <t>[2458.64, 2148.88, 890.11]</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>[977.96, 287.25, 477.49]</t>
+          <t>[2428.74, 2033.61, 833.88]</t>
         </is>
       </c>
     </row>
@@ -7014,31 +7014,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>79.28</v>
+        <v>70.78</v>
       </c>
       <c r="E183" t="n">
-        <v>70.37</v>
+        <v>54.65</v>
       </c>
       <c r="F183" t="n">
-        <v>15.75</v>
+        <v>3.95</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[307.75, 370.48, 388.87]</t>
+          <t>[2143.95, 887.31, 1068.65]</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>[287.25, 477.49, 472.46]</t>
+          <t>[2033.61, 833.88, 1068.47]</t>
         </is>
       </c>
     </row>
@@ -7050,31 +7050,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>85.3</v>
+        <v>33.02</v>
       </c>
       <c r="E184" t="n">
-        <v>80.48</v>
+        <v>27.35</v>
       </c>
       <c r="F184" t="n">
-        <v>16.78</v>
+        <v>2.77</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[366.54, 384.82, 543.63]</t>
+          <t>[884.94, 1062.55, 1498.56]</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[477.49, 472.46, 500.77]</t>
+          <t>[833.88, 1068.47, 1523.63]</t>
         </is>
       </c>
     </row>
@@ -7086,31 +7086,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>81.78</v>
+        <v>116.84</v>
       </c>
       <c r="E185" t="n">
-        <v>79.03</v>
+        <v>80.58</v>
       </c>
       <c r="F185" t="n">
-        <v>11.62</v>
+        <v>7.07</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[390.54, 552.74, 1548.59]</t>
+          <t>[1069.45, 1480.63, 882.3]</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[472.46, 500.77, 1445.38]</t>
+          <t>[1068.47, 1523.63, 1080.05]</t>
         </is>
       </c>
     </row>
@@ -7122,31 +7122,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>200.41</v>
+        <v>119.51</v>
       </c>
       <c r="E186" t="n">
-        <v>164.63</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="F186" t="n">
-        <v>11.84</v>
+        <v>8.32</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[556.11, 1561.53, 2283.3]</t>
+          <t>[1490.53, 876.07, 295.19]</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>[500.77, 1445.38, 1960.9]</t>
+          <t>[1523.63, 1080.05, 307.15]</t>
         </is>
       </c>
     </row>
@@ -7158,31 +7158,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>194.02</v>
+        <v>159.85</v>
       </c>
       <c r="E187" t="n">
-        <v>160.08</v>
+        <v>134.04</v>
       </c>
       <c r="F187" t="n">
-        <v>8.65</v>
+        <v>18.55</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[1556.2, 2272.92, 2486.12]</t>
+          <t>[879.66, 296.14, 378.32]</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[1445.38, 1960.9, 2428.74]</t>
+          <t>[1080.05, 307.15, 569.05]</t>
         </is>
       </c>
     </row>
@@ -7194,31 +7194,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>200.99</v>
+        <v>127.8</v>
       </c>
       <c r="E188" t="n">
-        <v>169.46</v>
+        <v>105.04</v>
       </c>
       <c r="F188" t="n">
-        <v>8.380000000000001</v>
+        <v>19.54</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[2275.18, 2483.48, 2172.97]</t>
+          <t>[297.94, 383.52, 402.35]</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[1960.9, 2428.74, 2033.61]</t>
+          <t>[307.15, 569.05, 522.74]</t>
         </is>
       </c>
     </row>
@@ -7230,31 +7230,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>76.03</v>
+        <v>127.46</v>
       </c>
       <c r="E189" t="n">
-        <v>67.13</v>
+        <v>106.7</v>
       </c>
       <c r="F189" t="n">
-        <v>4.55</v>
+        <v>19.48</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>[2458.64, 2148.88, 890.11]</t>
+          <t>[384.11, 403.21, 521.88]</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>[2428.74, 2033.61, 833.88]</t>
+          <t>[569.05, 522.74, 506.27]</t>
         </is>
       </c>
     </row>
@@ -7266,31 +7266,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>70.78</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="E190" t="n">
-        <v>54.65</v>
+        <v>49.53</v>
       </c>
       <c r="F190" t="n">
-        <v>3.95</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[2143.95, 887.31, 1068.65]</t>
+          <t>[413.48, 535.36, 1534.44]</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>[2033.61, 833.88, 1068.47]</t>
+          <t>[522.74, 506.27, 1524.19]</t>
         </is>
       </c>
     </row>
@@ -7302,31 +7302,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>33.02</v>
+        <v>129.64</v>
       </c>
       <c r="E191" t="n">
-        <v>27.35</v>
+        <v>97.14</v>
       </c>
       <c r="F191" t="n">
-        <v>2.77</v>
+        <v>6.84</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>[884.94, 1062.55, 1498.56]</t>
+          <t>[543.89, 1559.42, 2249.29]</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>[833.88, 1068.47, 1523.63]</t>
+          <t>[506.27, 1524.19, 2030.74]</t>
         </is>
       </c>
     </row>
@@ -7338,31 +7338,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>955.14</v>
+        <v>962.24</v>
       </c>
       <c r="E192" t="n">
-        <v>937.1900000000001</v>
+        <v>792.83</v>
       </c>
       <c r="F192" t="n">
-        <v>39.84</v>
+        <v>19.52</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[2980.09, 3338.53, 3536.74]</t>
+          <t>[1978.81, 2678.68, 3217.59]</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>[2303.08, 2285.14, 2455.58]</t>
+          <t>[1955.9, 3893.88, 4357.98]</t>
         </is>
       </c>
     </row>
@@ -7374,31 +7374,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>850.41</v>
+        <v>1470.89</v>
       </c>
       <c r="E193" t="n">
-        <v>849.4</v>
+        <v>1450.02</v>
       </c>
       <c r="F193" t="n">
-        <v>37.49</v>
+        <v>30.7</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>[3189.92, 3293.84, 2883.48]</t>
+          <t>[2589.53, 3109.94, 4200.97]</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[2285.14, 2455.58, 2078.31]</t>
+          <t>[3893.88, 4357.98, 5998.64]</t>
         </is>
       </c>
     </row>
@@ -7410,31 +7410,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>531.03</v>
+        <v>2144.76</v>
       </c>
       <c r="E194" t="n">
-        <v>473.77</v>
+        <v>1944.8</v>
       </c>
       <c r="F194" t="n">
-        <v>21.5</v>
+        <v>29.14</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>[3094.89, 2725.74, 1971.35]</t>
+          <t>[3270.27, 4447.3, 5538.18]</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>[2455.58, 2078.31, 1836.76]</t>
+          <t>[4357.98, 5998.64, 8733.53]</t>
         </is>
       </c>
     </row>
@@ -7446,31 +7446,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>541.34</v>
+        <v>1893.36</v>
       </c>
       <c r="E195" t="n">
-        <v>482.14</v>
+        <v>1539.2</v>
       </c>
       <c r="F195" t="n">
-        <v>22.7</v>
+        <v>22.47</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>[2740.0, 1970.86, 2897.47]</t>
+          <t>[4606.8, 5776.32, 2330.2]</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>[2078.31, 1836.76, 2246.84]</t>
+          <t>[5998.64, 8733.53, 2598.76]</t>
         </is>
       </c>
     </row>
@@ -7482,31 +7482,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>590.89</v>
+        <v>1705.56</v>
       </c>
       <c r="E196" t="n">
-        <v>506.79</v>
+        <v>1114.51</v>
       </c>
       <c r="F196" t="n">
-        <v>23.82</v>
+        <v>16.3</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[1939.79, 2828.24, 2927.23]</t>
+          <t>[5793.84, 2355.33, 2892.65]</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>[1836.76, 2246.84, 2091.29]</t>
+          <t>[8733.53, 2598.76, 2732.23]</t>
         </is>
       </c>
     </row>
@@ -7518,31 +7518,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>596.71</v>
+        <v>255.18</v>
       </c>
       <c r="E197" t="n">
-        <v>527.12</v>
+        <v>248.19</v>
       </c>
       <c r="F197" t="n">
-        <v>24.73</v>
+        <v>9.25</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[2832.58, 2927.82, 2114.99]</t>
+          <t>[2342.54, 2904.11, 3043.13]</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[2246.84, 2091.29, 1955.9]</t>
+          <t>[2598.76, 2732.23, 2726.66]</t>
         </is>
       </c>
     </row>
@@ -7554,31 +7554,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>776.53</v>
+        <v>236.78</v>
       </c>
       <c r="E198" t="n">
-        <v>649.1799999999999</v>
+        <v>213.49</v>
       </c>
       <c r="F198" t="n">
-        <v>22.89</v>
+        <v>7.89</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[2834.78, 2042.47, 2776.42]</t>
+          <t>[2925.23, 3074.55, 2679.28]</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>[2091.29, 1955.9, 3893.88]</t>
+          <t>[2732.23, 2726.66, 2579.69]</t>
         </is>
       </c>
     </row>
@@ -7590,31 +7590,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>962.24</v>
+        <v>206.62</v>
       </c>
       <c r="E199" t="n">
-        <v>792.83</v>
+        <v>173.62</v>
       </c>
       <c r="F199" t="n">
-        <v>19.52</v>
+        <v>6.98</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[1978.81, 2678.68, 3217.59]</t>
+          <t>[3058.23, 2663.74, 2007.34]</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[1955.9, 3893.88, 4357.98]</t>
+          <t>[2726.66, 2579.69, 1902.11]</t>
         </is>
       </c>
     </row>
@@ -7626,31 +7626,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1470.89</v>
+        <v>408.88</v>
       </c>
       <c r="E200" t="n">
-        <v>1450.02</v>
+        <v>289.07</v>
       </c>
       <c r="F200" t="n">
-        <v>30.7</v>
+        <v>13.16</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[2589.53, 3109.94, 4200.97]</t>
+          <t>[2653.02, 1998.18, 2906.17]</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>[3893.88, 4357.98, 5998.64]</t>
+          <t>[2579.69, 1902.11, 2208.35]</t>
         </is>
       </c>
     </row>
@@ -7662,31 +7662,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2144.76</v>
+        <v>475.66</v>
       </c>
       <c r="E201" t="n">
-        <v>1944.8</v>
+        <v>407.53</v>
       </c>
       <c r="F201" t="n">
-        <v>29.14</v>
+        <v>18.5</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[3270.27, 4447.3, 5538.18]</t>
+          <t>[1996.08, 2901.19, 2708.52]</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>[4357.98, 5998.64, 8733.53]</t>
+          <t>[1902.11, 2208.35, 2272.74]</t>
         </is>
       </c>
     </row>
